--- a/data/trans_camb/P16A10-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,4</t>
+          <t>-3,51; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,51</t>
+          <t>-1,67; 3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,37</t>
+          <t>-1,29; 3,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,76</t>
+          <t>-2,0; 3,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,38</t>
+          <t>-0,93; 4,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,77</t>
+          <t>-0,29; 4,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,47</t>
+          <t>-1,82; 1,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,12</t>
+          <t>-0,56; 3,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,03</t>
+          <t>-0,08; 3,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 32,58</t>
+          <t>-50,43; 32,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 76,55</t>
+          <t>-25,18; 85,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 76,83</t>
+          <t>-21,17; 77,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 68,97</t>
+          <t>-31,55; 78,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 107,9</t>
+          <t>-15,56; 108,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 93,07</t>
+          <t>-5,46; 105,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 31,46</t>
+          <t>-29,41; 34,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 70,04</t>
+          <t>-9,35; 67,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 68,89</t>
+          <t>-2,5; 69,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,19</t>
+          <t>-3,45; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,74</t>
+          <t>-2,56; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; -0,92</t>
+          <t>-5,53; -0,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,46</t>
+          <t>-2,54; 1,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,7</t>
+          <t>-2,42; 1,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,98</t>
+          <t>-2,43; 1,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,68</t>
+          <t>-2,2; 0,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,11</t>
+          <t>-1,73; 1,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,45</t>
+          <t>-3,48; -0,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 24,67</t>
+          <t>-46,83; 15,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 36,76</t>
+          <t>-35,8; 35,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,1; -17,65</t>
+          <t>-75,55; -16,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,1; 34,71</t>
+          <t>-39,37; 34,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,11; 38,6</t>
+          <t>-38,08; 39,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 24,92</t>
+          <t>-36,28; 27,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 13,02</t>
+          <t>-34,58; 16,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 23,97</t>
+          <t>-27,12; 23,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,45; -10,07</t>
+          <t>-53,12; -9,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,91</t>
+          <t>-2,94; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,28</t>
+          <t>-1,6; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,67</t>
+          <t>-1,46; 3,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,73</t>
+          <t>-3,4; 1,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,11</t>
+          <t>-1,67; 3,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,39</t>
+          <t>-4,52; 0,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,75</t>
+          <t>-2,51; 0,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,67</t>
+          <t>-1,22; 2,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,18</t>
+          <t>-2,82; 1,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 44,1</t>
+          <t>-45,0; 47,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 81,06</t>
+          <t>-23,76; 83,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 86,79</t>
+          <t>-22,23; 93,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 20,72</t>
+          <t>-56,2; 28,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 82,17</t>
+          <t>-26,86; 92,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 8,44</t>
+          <t>-70,62; 6,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 16,46</t>
+          <t>-41,97; 13,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 61,99</t>
+          <t>-18,42; 53,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 25,1</t>
+          <t>-46,39; 24,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,14</t>
+          <t>-0,31; 3,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,93</t>
+          <t>-0,73; 3,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,77</t>
+          <t>-0,09; 3,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,52</t>
+          <t>-2,59; 1,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,88</t>
+          <t>-3,1; 0,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,65</t>
+          <t>-2,32; 1,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,88</t>
+          <t>-0,83; 2,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,37</t>
+          <t>-1,33; 1,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,88</t>
+          <t>-0,82; 1,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 113,42</t>
+          <t>-6,22; 104,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 75,82</t>
+          <t>-13,66; 78,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 101,17</t>
+          <t>-1,54; 97,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 33,69</t>
+          <t>-39,7; 33,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 20,08</t>
+          <t>-48,2; 21,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 36,71</t>
+          <t>-33,88; 38,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 41,74</t>
+          <t>-14,67; 45,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 32,03</t>
+          <t>-23,2; 34,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 42,25</t>
+          <t>-13,77; 42,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,01</t>
+          <t>-1,17; 1,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,62</t>
+          <t>-0,64; 1,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,06</t>
+          <t>-1,56; 1,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,53</t>
+          <t>-1,54; 0,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,17</t>
+          <t>-0,99; 1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,57</t>
+          <t>-1,58; 0,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,46</t>
+          <t>-1,03; 0,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,16</t>
+          <t>-0,48; 1,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,59</t>
+          <t>-1,04; 0,64</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 21,11</t>
+          <t>-19,8; 21,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 34,73</t>
+          <t>-10,95; 32,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 21,54</t>
+          <t>-27,05; 21,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 11,11</t>
+          <t>-26,0; 13,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 23,83</t>
+          <t>-17,16; 26,76</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 11,78</t>
+          <t>-27,0; 12,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 9,16</t>
+          <t>-18,15; 9,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 23,62</t>
+          <t>-8,42; 22,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 11,46</t>
+          <t>-18,23; 12,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A10-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,41</t>
+          <t>-3,22; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,65</t>
+          <t>-1,6; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,45</t>
+          <t>-1,01; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,16</t>
+          <t>-1,89; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,44</t>
+          <t>-0,91; 4,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,12</t>
+          <t>-0,39; 3,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,48</t>
+          <t>-1,81; 1,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,11</t>
+          <t>-0,77; 3,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,19</t>
+          <t>-0,07; 3,21</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 32,48</t>
+          <t>-46,85; 32,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 85,44</t>
+          <t>-23,43; 78,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 77,29</t>
+          <t>-15,2; 81,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 78,46</t>
+          <t>-31,85; 74,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 108,31</t>
+          <t>-15,87; 102,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 105,99</t>
+          <t>-6,81; 98,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 34,14</t>
+          <t>-29,45; 33,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 67,87</t>
+          <t>-12,65; 67,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 69,95</t>
+          <t>-1,46; 69,6</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,8</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,81</t>
+          <t>-2,98; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,77</t>
+          <t>-2,47; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,9</t>
+          <t>-3,76; -0,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,45</t>
+          <t>-2,68; 1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,71</t>
+          <t>-2,27; 1,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,14</t>
+          <t>-2,58; 0,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,84</t>
+          <t>-2,4; 0,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,13</t>
+          <t>-1,72; 1,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,47</t>
+          <t>-2,5; -0,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-46,47%</t>
+          <t>-32,27%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,03%</t>
+          <t>-13,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-31,64%</t>
+          <t>-23,36%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 15,43</t>
+          <t>-43,59; 23,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 35,24</t>
+          <t>-35,21; 39,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,55; -16,1</t>
+          <t>-52,11; -3,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 34,0</t>
+          <t>-40,48; 32,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 39,22</t>
+          <t>-36,32; 41,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 27,8</t>
+          <t>-40,26; 21,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 16,41</t>
+          <t>-36,7; 11,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 23,1</t>
+          <t>-26,68; 27,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,12; -9,33</t>
+          <t>-39,01; -2,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,88</t>
+          <t>-3,05; 1,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,41</t>
+          <t>-1,78; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,77</t>
+          <t>-1,3; 3,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,0</t>
+          <t>-3,52; 0,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,1</t>
+          <t>-1,57; 3,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,35</t>
+          <t>-2,49; 1,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,57</t>
+          <t>-2,74; 0,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,38</t>
+          <t>-1,07; 2,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,08</t>
+          <t>-1,48; 1,81</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-33,81%</t>
+          <t>-11,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,15%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 47,24</t>
+          <t>-46,72; 36,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 83,18</t>
+          <t>-26,4; 74,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 93,66</t>
+          <t>-20,81; 75,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,2; 28,48</t>
+          <t>-55,75; 19,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 92,26</t>
+          <t>-28,11; 88,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 6,19</t>
+          <t>-40,7; 35,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 13,44</t>
+          <t>-43,93; 18,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 53,94</t>
+          <t>-18,27; 56,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 24,04</t>
+          <t>-23,74; 41,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,97</t>
+          <t>-0,2; 4,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,02</t>
+          <t>-0,62; 3,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,68</t>
+          <t>-0,17; 3,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,5</t>
+          <t>-2,47; 1,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,98</t>
+          <t>-2,87; 1,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,61</t>
+          <t>-1,72; 1,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,01</t>
+          <t>-0,91; 2,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,46</t>
+          <t>-1,44; 1,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,86</t>
+          <t>-0,38; 2,17</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 104,93</t>
+          <t>-4,69; 107,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 78,28</t>
+          <t>-12,81; 85,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 97,87</t>
+          <t>-4,8; 92,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 33,1</t>
+          <t>-37,42; 31,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 21,27</t>
+          <t>-45,12; 26,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,88; 38,16</t>
+          <t>-26,31; 44,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 45,55</t>
+          <t>-16,35; 44,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 34,3</t>
+          <t>-24,36; 32,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 42,24</t>
+          <t>-6,38; 49,85</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,04</t>
+          <t>-1,28; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,59</t>
+          <t>-0,63; 1,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,07</t>
+          <t>-0,75; 1,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,61</t>
+          <t>-1,6; 0,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,26</t>
+          <t>-1,08; 1,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,57</t>
+          <t>-1,02; 0,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,46</t>
+          <t>-1,0; 0,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,11</t>
+          <t>-0,42; 1,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,64</t>
+          <t>-0,53; 0,94</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-0,36%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-7,3%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-3,9%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 21,89</t>
+          <t>-21,4; 20,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 32,54</t>
+          <t>-10,59; 33,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 21,93</t>
+          <t>-12,14; 27,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 13,5</t>
+          <t>-27,38; 11,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 26,76</t>
+          <t>-18,71; 24,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 12,23</t>
+          <t>-16,84; 19,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 9,24</t>
+          <t>-17,56; 9,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 22,24</t>
+          <t>-7,41; 22,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 12,94</t>
+          <t>-9,27; 19,29</t>
         </is>
       </c>
     </row>
